--- a/Plotting/Results_excels/production_shares_olefins_Scope1-2.xlsx
+++ b/Plotting/Results_excels/production_shares_olefins_Scope1-2.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,13 +483,6 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Iteration_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -542,26 +535,11 @@
           <t>2050</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -591,20 +569,11 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -632,15 +601,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -660,31 +620,22 @@
         <v>1052661.907550473</v>
       </c>
       <c r="E6" t="n">
-        <v>1717666.256705084</v>
+        <v>1717666.256705102</v>
       </c>
       <c r="F6" t="n">
-        <v>1291202.896779111</v>
+        <v>1291552.741934005</v>
       </c>
       <c r="G6" t="n">
-        <v>1714830.272471079</v>
+        <v>1717666.256705089</v>
       </c>
       <c r="H6" t="n">
-        <v>1717666.256705097</v>
+        <v>1717666.256705121</v>
       </c>
       <c r="I6" t="n">
-        <v>1290346.75326915</v>
+        <v>1290999.237592817</v>
       </c>
       <c r="J6" t="n">
-        <v>1698077.064036473</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1717666.256705082</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1291233.819577181</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1698285.997250964</v>
+        <v>1717666.256705119</v>
       </c>
     </row>
     <row r="7">
@@ -720,15 +671,6 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -749,28 +691,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>426374.9082661472</v>
+        <v>426025.1356717293</v>
       </c>
       <c r="G8" t="n">
-        <v>2835.396029873991</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>427230.8742055938</v>
+        <v>426578.5252120138</v>
       </c>
       <c r="J8" t="n">
-        <v>19585.12972495666</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>426343.9918816964</v>
-      </c>
-      <c r="M8" t="n">
-        <v>19376.23984474674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -806,15 +739,6 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -849,15 +773,6 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -892,15 +807,6 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -935,15 +841,6 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -978,15 +875,6 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1021,15 +909,6 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1064,15 +943,6 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1107,22 +977,12 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
